--- a/CONSOLIDADO_CONTRATISTAS_PLANTABAL.xlsx
+++ b/CONSOLIDADO_CONTRATISTAS_PLANTABAL.xlsx
@@ -12,7 +12,7 @@
     <sheet name="MAESTRO EMPRESAS" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">CONSOLIDADO!$A$3:$P$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">CONSOLIDADO!$A$4:$P$4</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
   <si>
     <t xml:space="preserve">PLANTABAL S.A. / 3A CORE MATERIALS
 CONSOLIDADO DE CONTRATISTAS — Control de Acceso y Habilitaciones</t>
@@ -33,6 +33,9 @@
     <t xml:space="preserve">Responsable: Héctor Clavijo  |  Planta: Quevedo y Santo Domingo  |  Actualizado: 28/10/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">🟢 APTO / Vigente   🔴 NO APTO / Vencido   🟡 Por vencer (&lt; 30 días)   | Aptitud: escriba APTO o NO APTO  | Fechas: ingresar en formato DD/MM/AAAA</t>
+  </si>
+  <si>
     <t xml:space="preserve">N°</t>
   </si>
   <si>
@@ -60,48 +63,82 @@
 (Caducidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cert. Prevención Riesgos Eléctricos
+    <t xml:space="preserve">Cert. Prevención
+Riesgos Eléctricos
 (Caducidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cert. Trabajos en Altura
+    <t xml:space="preserve">Cert. Trabajos
+en Altura
 (Caducidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cert. Espacios Confinados
+    <t xml:space="preserve">Cert. Espacios
+Confinados
 (Caducidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cert. Trabajos en Caliente
+    <t xml:space="preserve">Cert. Trabajos
+en Caliente
 (Caducidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cert. Prevención de Riesgos
+    <t xml:space="preserve">Cert. Prevención
+de Riesgos
 (Caducidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Curso Primeros Auxilios
+    <t xml:space="preserve">Curso Primeros
+Auxilios
 (Fecha emisión)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aptitud de Ingreso</t>
+    <t xml:space="preserve">Aptitud de
+Ingreso</t>
   </si>
   <si>
     <t xml:space="preserve">Observaciones</t>
   </si>
   <si>
+    <t xml:space="preserve">PLANTABAL S.A. — Lista Maestra de Empresas Contratistas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de la Empresa / Contratista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encargado / Representante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado</t>
+  </si>
+  <si>
     <t xml:space="preserve">FRANKMETAL S.A.S.</t>
   </si>
   <si>
+    <t xml:space="preserve">Francisco Macías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Industrias Don Quiño</t>
   </si>
   <si>
+    <t xml:space="preserve">Dailer Quiñonez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taller industrial Don Remigio</t>
   </si>
   <si>
+    <t xml:space="preserve">Remigio Chalacama</t>
+  </si>
+  <si>
     <t xml:space="preserve">MP - Servicios profesionales</t>
   </si>
   <si>
+    <t xml:space="preserve">Michael Pallo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jonny Lam</t>
   </si>
   <si>
@@ -111,27 +148,51 @@
     <t xml:space="preserve">La Llave</t>
   </si>
   <si>
+    <t xml:space="preserve">Jorge Escobar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Firewall</t>
   </si>
   <si>
+    <t xml:space="preserve">Wilson Pastuisaca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taller industrial Asimbaya</t>
   </si>
   <si>
+    <t xml:space="preserve">José Asimbaya</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taller industrial Chávez</t>
   </si>
   <si>
+    <t xml:space="preserve">Cristian Chávez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Proinseg</t>
   </si>
   <si>
+    <t xml:space="preserve">Juan Barrionuevo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frío Aycart</t>
   </si>
   <si>
+    <t xml:space="preserve">Yordan Aycart</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sosa</t>
   </si>
   <si>
+    <t xml:space="preserve">Carlos Sosa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Meta technologie</t>
   </si>
   <si>
+    <t xml:space="preserve">Ricardo Burbano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wilmer Salazar</t>
   </si>
   <si>
@@ -141,100 +202,25 @@
     <t xml:space="preserve">ISEP</t>
   </si>
   <si>
+    <t xml:space="preserve">Emiliano Crespo</t>
+  </si>
+  <si>
     <t xml:space="preserve">JC</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonathan Cedeño</t>
+  </si>
+  <si>
     <t xml:space="preserve">Julio Cano</t>
   </si>
   <si>
     <t xml:space="preserve">ISMI</t>
   </si>
   <si>
+    <t xml:space="preserve">Borys Jonathan Palma Tasinchano</t>
+  </si>
+  <si>
     <t xml:space="preserve">ASOSERLIMFESA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📋  INSTRUCCIONES: Complete las celdas en AMARILLO con la información de cada colaborador. Apellido, Nombres, N° Cédula y fechas de caducidad/emisión de cada certificado. La columna 'Empresa/Compañía' ya está prellenada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apellido Apellido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0901234567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin novedad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLANTABAL S.A. — Lista Maestra de Empresas Contratistas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de la Empresa / Contratista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encargado / Representante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francisco Macías</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dailer Quiñonez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remigio Chalacama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Pallo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jorge Escobar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson Pastuisaca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">José Asimbaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristian Chávez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Barrionuevo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yordan Aycart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Sosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricardo Burbano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emiliano Crespo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Cedeño</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borys Jonathan Palma Tasinchano</t>
   </si>
   <si>
     <t xml:space="preserve">Quishpe Calderón Edison Angel</t>
@@ -248,7 +234,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +274,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
@@ -298,28 +292,13 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
+      <color rgb="FF9E9E9E"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF1A3A6B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -341,7 +320,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,13 +330,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFDE7"/>
+        <bgColor rgb="FFFFF9E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -368,26 +353,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFDE7"/>
+        <fgColor rgb="FFFFF9E6"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6E4F7"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEBF5FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -461,7 +434,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -478,27 +451,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -506,39 +467,35 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -551,19 +508,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF2E6DB4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD6E4F7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -577,25 +526,89 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF276221"/>
+        <sz val="9"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+        <sz val="9"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF9C5700"/>
+        <sz val="9"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1A3A6B"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF9C0006"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF9C5700"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF276221"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -610,8 +623,8 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF9C0006"/>
+      <rgbColor rgb="FF276221"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -620,8 +633,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFFFF9E6"/>
+      <rgbColor rgb="FFEBF5FB"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -635,13 +648,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF5F5F5"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFC6EFCE"/>
+      <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF2E6DB4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -649,12 +662,12 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF9E9E9E"/>
       <rgbColor rgb="FF1A3A6B"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF9C5700"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -716,9 +729,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>815040</xdr:colOff>
+      <xdr:colOff>910080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>428400</xdr:rowOff>
+      <xdr:rowOff>475920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -732,7 +745,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1238040" cy="428400"/>
+          <a:ext cx="1333080" cy="475920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -927,20 +940,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -983,88 +995,84 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="P4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -1074,19 +1082,17 @@
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="6"/>
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -1096,19 +1102,17 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="6"/>
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -1118,19 +1122,17 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="6"/>
+      <c r="A8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -1140,19 +1142,17 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="6"/>
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -1162,19 +1162,17 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="6"/>
+      <c r="A10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
@@ -1184,19 +1182,17 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="6"/>
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -1206,19 +1202,17 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="6"/>
+      <c r="A12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
@@ -1228,19 +1222,17 @@
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="6"/>
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -1250,19 +1242,17 @@
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="6"/>
+      <c r="A14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -1272,19 +1262,17 @@
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="6"/>
+      <c r="A15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -1294,19 +1282,17 @@
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="6"/>
+      <c r="A16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -1316,19 +1302,17 @@
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="6"/>
+      <c r="A17" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -1338,19 +1322,17 @@
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="6"/>
+      <c r="A18" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -1360,19 +1342,17 @@
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="6"/>
+      <c r="A19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1382,19 +1362,17 @@
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="6"/>
+      <c r="A20" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -1404,19 +1382,17 @@
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="6"/>
+      <c r="A21" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -1426,19 +1402,17 @@
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="6"/>
+      <c r="A22" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -1448,19 +1422,17 @@
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="6"/>
+      <c r="A23" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1470,19 +1442,17 @@
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="6"/>
+      <c r="A24" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -1492,87 +1462,727 @@
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="12" t="s">
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F27" s="13" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>46310</v>
-      </c>
-      <c r="H27" s="13" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I27" s="12" t="s">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="J27" s="13" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M27" s="13" t="n">
-        <v>46096</v>
-      </c>
-      <c r="N27" s="13" t="n">
-        <v>45981</v>
-      </c>
-      <c r="O27" s="12" t="s">
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="P27" s="12" t="s">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="n">
         <v>46</v>
       </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P24"/>
+  <autoFilter ref="A4:P4"/>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:P1"/>
     <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A26:P26"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
+  <conditionalFormatting sqref="O5:O54">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>"APTO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>"NO APTO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>"PENDIENTE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F54">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(F5&lt;&gt;"",ISNUMBER(F5),F5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(F5&lt;&gt;"",ISNUMBER(F5),F5&gt;=TODAY(),F5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(F5&lt;&gt;"",ISNUMBER(F5),F5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G54">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(G5&lt;&gt;"",ISNUMBER(G5),G5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(G5&lt;&gt;"",ISNUMBER(G5),G5&gt;=TODAY(),G5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(G5&lt;&gt;"",ISNUMBER(G5),G5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H54">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(H5&lt;&gt;"",ISNUMBER(H5),H5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(H5&lt;&gt;"",ISNUMBER(H5),H5&gt;=TODAY(),H5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(H5&lt;&gt;"",ISNUMBER(H5),H5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I54">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(I5&lt;&gt;"",ISNUMBER(I5),I5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(I5&lt;&gt;"",ISNUMBER(I5),I5&gt;=TODAY(),I5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(I5&lt;&gt;"",ISNUMBER(I5),I5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J54">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(J5&lt;&gt;"",ISNUMBER(J5),J5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(J5&lt;&gt;"",ISNUMBER(J5),J5&gt;=TODAY(),J5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(J5&lt;&gt;"",ISNUMBER(J5),J5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K54">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(K5&lt;&gt;"",ISNUMBER(K5),K5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(K5&lt;&gt;"",ISNUMBER(K5),K5&gt;=TODAY(),K5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(K5&lt;&gt;"",ISNUMBER(K5),K5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L5:L54">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(L5&lt;&gt;"",ISNUMBER(L5),L5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(L5&lt;&gt;"",ISNUMBER(L5),L5&gt;=TODAY(),L5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(L5&lt;&gt;"",ISNUMBER(L5),L5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M54">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(M5&lt;&gt;"",ISNUMBER(M5),M5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(M5&lt;&gt;"",ISNUMBER(M5),M5&gt;=TODAY(),M5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(M5&lt;&gt;"",ISNUMBER(M5),M5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N54">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(N5&lt;&gt;"",ISNUMBER(N5),N5&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(N5&lt;&gt;"",ISNUMBER(N5),N5&gt;=TODAY(),N5&lt;=TODAY()+30)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(N5&lt;&gt;"",ISNUMBER(N5),N5&gt;TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1594,322 +2204,322 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+    <row r="1" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-    </row>
-    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="15" t="s">
+      <c r="D15" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C16" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D16" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="C17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="B20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="B21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="B22" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="19" t="s">
+      <c r="B23" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
